--- a/data/IKPA_MARET_2025.xlsx
+++ b/data/IKPA_MARET_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X69"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,10 +541,15 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Uraian Satker Final</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Satker</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -566,7 +571,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>'007130</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -631,10 +636,15 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU (007130)</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>KEJARI  OKU ('007130)</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -642,7 +652,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -651,17 +661,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -683,10 +693,10 @@
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
@@ -695,11 +705,11 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -721,10 +731,15 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR (007190)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666503)</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -732,7 +747,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -741,17 +756,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -773,10 +788,10 @@
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -785,11 +800,11 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -811,10 +826,15 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA (527975)</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -822,7 +842,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -831,17 +851,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -863,7 +883,7 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -875,11 +895,11 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -901,10 +921,15 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (098963)</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUS (553792)</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -912,7 +937,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -921,17 +946,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>'007190</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -953,10 +978,10 @@
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -965,11 +990,11 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -991,10 +1016,15 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (099228)</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>KEJARI OKUT ('007190)</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1002,7 +1032,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1016,12 +1046,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1081,10 +1111,15 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (111071)</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
+        <is>
+          <t>MAN 2 OKUS (597558)</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1092,7 +1127,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1101,17 +1136,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1133,10 +1168,10 @@
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1145,11 +1180,11 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R8" t="n">
@@ -1171,10 +1206,15 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR (111079)</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
+        <is>
+          <t>POLRES OKU (641681)</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1182,7 +1222,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1191,17 +1231,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1223,10 +1263,10 @@
         <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>100</v>
@@ -1235,11 +1275,11 @@
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -1261,10 +1301,15 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ (344894)</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
+        <is>
+          <t>KPU OKU (656553)</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1272,7 +1317,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1281,17 +1326,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1313,10 +1358,10 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1325,11 +1370,11 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1351,10 +1396,15 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (401944)</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
+        <is>
+          <t>KPU OKUS (656574)</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1362,7 +1412,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1371,17 +1421,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1403,10 +1453,10 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>100</v>
@@ -1415,11 +1465,11 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1441,10 +1491,15 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUS (661192)</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1452,7 +1507,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1461,17 +1516,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1531,10 +1586,15 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
+        <is>
+          <t>POLRES OKUT (665292)</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1542,7 +1602,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1551,17 +1611,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1621,10 +1681,15 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
+        <is>
+          <t>POLRES OKUS (665307)</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1632,7 +1697,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1641,17 +1706,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1673,10 +1738,10 @@
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>100</v>
@@ -1685,11 +1750,11 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -1711,10 +1776,15 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666501)</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1722,7 +1792,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1731,17 +1801,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1763,10 +1833,10 @@
         <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
@@ -1775,11 +1845,11 @@
         <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -1801,10 +1871,15 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (403410)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666502)</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1812,7 +1887,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1821,17 +1896,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1853,7 +1928,7 @@
         <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1865,11 +1940,11 @@
         <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R16" t="n">
@@ -1891,10 +1966,15 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666504)</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1902,7 +1982,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1916,12 +1996,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1981,10 +2061,15 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418457)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440506)</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1992,7 +2077,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2006,12 +2091,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2071,10 +2156,15 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418459)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666505)</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2082,7 +2172,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2096,12 +2186,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2161,10 +2251,15 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418461)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666507)</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2172,7 +2267,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2181,17 +2276,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2213,10 +2308,10 @@
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" t="n">
         <v>100</v>
@@ -2225,11 +2320,11 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -2251,10 +2346,15 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (418462)</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
+        <is>
+          <t>BPS OKUS (667215)</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2262,7 +2362,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2271,17 +2371,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2303,10 +2403,10 @@
         <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
         <v>100</v>
@@ -2315,11 +2415,11 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -2341,10 +2441,15 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR (418471)</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
+        <is>
+          <t>BPS OKUT (668529)</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2352,7 +2457,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2361,17 +2466,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2431,10 +2536,15 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU (419006)</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
+        <is>
+          <t>BPN OKUT (669055)</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2442,7 +2552,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2451,17 +2561,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2521,10 +2631,15 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU (424245)</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
+        <is>
+          <t>BPN OKUS (670561)</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2532,7 +2647,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2541,17 +2656,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2573,7 +2688,7 @@
         <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2585,11 +2700,11 @@
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="R24" t="n">
@@ -2611,10 +2726,15 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (424967)</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
+        <is>
+          <t>LOKA LABKESMAS (690801)</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2622,7 +2742,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2631,17 +2751,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2663,10 +2783,10 @@
         <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -2675,11 +2795,11 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -2701,10 +2821,15 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU (426050)</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
+        <is>
+          <t>LAPAS MUARA DUA (692334)</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2712,7 +2837,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2721,17 +2846,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2753,10 +2878,10 @@
         <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
         <v>100</v>
@@ -2765,11 +2890,11 @@
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R26" t="n">
@@ -2791,10 +2916,15 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (426066)</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
+        <is>
+          <t>RUTAN BATURAJA (692339)</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2802,7 +2932,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2811,17 +2941,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2881,10 +3011,15 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
+        <is>
+          <t>LAPAS MARTAPURA (692340)</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2892,7 +3027,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2901,17 +3036,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2971,10 +3106,15 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU (431142)</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
+        <is>
+          <t>BAPAS OKU INDUK (692625)</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2982,7 +3122,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2991,17 +3131,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3023,10 +3163,10 @@
         <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
@@ -3035,11 +3175,11 @@
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R29" t="n">
@@ -3061,10 +3201,15 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440502)</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
+        <is>
+          <t>RUPBASAN BATURAJA (692725)</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3072,7 +3217,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3086,7 +3231,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3151,10 +3296,15 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440504)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440507)</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3162,7 +3312,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3176,12 +3326,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3241,10 +3391,15 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440505)</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUS (574370)</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3252,7 +3407,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3266,7 +3421,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3331,10 +3486,15 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440506)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440505)</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3342,7 +3502,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3351,17 +3511,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -3383,7 +3543,7 @@
         <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3395,11 +3555,11 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -3421,10 +3581,15 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
+        <is>
+          <t>KPP BATURAJA (410574)</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3432,7 +3597,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3441,17 +3606,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>'007208</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -3473,10 +3638,10 @@
         <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34" t="n">
         <v>100</v>
@@ -3485,11 +3650,11 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -3511,10 +3676,15 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
+          <t>KEJARI  OKUS</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
+        <is>
+          <t>KEJARI  OKUS ('007208)</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3522,7 +3692,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3531,17 +3701,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>'098963</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -3563,7 +3733,7 @@
         <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3575,11 +3745,11 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -3601,10 +3771,15 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (553792)</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
+        <is>
+          <t>PN BATURAJA ('098963)</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3612,7 +3787,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3621,17 +3796,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>'099228</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -3691,10 +3866,15 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN (574370)</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
+        <is>
+          <t>PN BATURAJA ('099228)</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3702,7 +3882,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3716,12 +3896,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -3781,10 +3961,15 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (597558)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (111071)</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3792,7 +3977,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3801,17 +3986,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3833,10 +4018,10 @@
         <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>100</v>
@@ -3845,11 +4030,11 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -3871,10 +4056,15 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU (641681)</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
+        <is>
+          <t>BNN OKUT (111079)</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3882,7 +4072,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3891,17 +4081,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -3923,10 +4113,10 @@
         <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
@@ -3935,11 +4125,11 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3961,10 +4151,15 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU (656553)</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
+        <is>
+          <t>RUMKIT NOESMIR (344894)</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3972,7 +4167,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3981,17 +4176,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4013,10 +4208,10 @@
         <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -4025,11 +4220,11 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -4051,10 +4246,15 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN (656574)</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
+        <is>
+          <t>PA MARTAPURA (401944)</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4062,7 +4262,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4071,17 +4271,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4103,10 +4303,10 @@
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -4115,11 +4315,11 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -4141,10 +4341,15 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN (661192)</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
+        <is>
+          <t>PA MUARADUA (401945)</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4152,7 +4357,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4161,17 +4366,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4193,10 +4398,10 @@
         <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>100</v>
@@ -4205,11 +4410,11 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -4231,10 +4436,15 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR (665292)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440504)</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4242,7 +4452,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4251,17 +4461,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4321,10 +4531,15 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN (665307)</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
+        <is>
+          <t>PA BATURAJA (402268)</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4332,7 +4547,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4341,17 +4556,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4373,10 +4588,10 @@
         <v>100</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N44" t="n">
         <v>100</v>
@@ -4385,11 +4600,11 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -4411,10 +4626,15 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666501)</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
+        <is>
+          <t>PA MARTAPURA (403409)</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4422,7 +4642,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4431,17 +4651,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4463,10 +4683,10 @@
         <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
@@ -4475,11 +4695,11 @@
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -4501,10 +4721,15 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666502)</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
+        <is>
+          <t>PA  MUARADUA (403410)</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4512,7 +4737,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4521,17 +4746,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4553,10 +4778,10 @@
         <v>100</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N46" t="n">
         <v>100</v>
@@ -4565,11 +4790,11 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -4591,10 +4816,15 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
+        <is>
+          <t>PA BATURAJA (402267)</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4602,7 +4832,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4616,12 +4846,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4681,10 +4911,15 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666504)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418457)</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4692,7 +4927,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4706,12 +4941,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4771,10 +5006,15 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666505)</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUT (424967)</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4782,7 +5022,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4796,12 +5036,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -4861,10 +5101,15 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666507)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440502)</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4872,7 +5117,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4881,17 +5126,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -4913,10 +5158,10 @@
         <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>100</v>
@@ -4925,11 +5170,11 @@
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R50" t="n">
@@ -4951,10 +5196,15 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN (667215)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418459)</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4962,7 +5212,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4976,12 +5226,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5041,10 +5291,15 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR (668529)</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
+        <is>
+          <t>BPS OKU (428258)</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5052,7 +5307,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5061,17 +5316,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5131,10 +5386,15 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN (669055)</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUT (426066)</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5142,7 +5402,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5151,17 +5411,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5221,10 +5481,15 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN (670561)</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKU (426050)</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5232,7 +5497,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5241,17 +5506,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5273,7 +5538,7 @@
         <v>100</v>
       </c>
       <c r="L54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -5285,11 +5550,11 @@
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R54" t="n">
@@ -5311,10 +5576,15 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA (690801)</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
+        <is>
+          <t>BPN OKU (431142)</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5322,7 +5592,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5331,17 +5601,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5363,10 +5633,10 @@
         <v>100</v>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
         <v>100</v>
@@ -5375,11 +5645,11 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R55" t="n">
@@ -5401,10 +5671,15 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA (692334)</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU (424245)</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5412,7 +5687,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -5421,17 +5696,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5453,10 +5728,10 @@
         <v>100</v>
       </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -5465,11 +5740,11 @@
         <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R56" t="n">
@@ -5491,10 +5766,15 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA (692339)</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
+        <is>
+          <t>BAWASLU OKU (419006)</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5502,7 +5782,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -5511,17 +5791,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5543,10 +5823,10 @@
         <v>100</v>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>100</v>
@@ -5555,11 +5835,11 @@
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -5581,10 +5861,15 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA (692340)</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUT (418471)</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5592,7 +5877,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -5601,17 +5886,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5671,10 +5956,15 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK (692625)</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUS (418462)</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5682,7 +5972,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -5691,17 +5981,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>692725</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5723,10 +6013,10 @@
         <v>100</v>
       </c>
       <c r="L59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>100</v>
@@ -5735,11 +6025,11 @@
         <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R59" t="n">
@@ -5761,10 +6051,15 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA (692725)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418461)</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5851,10 +6146,15 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440503)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440503)</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5941,10 +6241,15 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN (686503)</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
+        <is>
+          <t>BAWASLU OKUS (686503)</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6031,10 +6336,15 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD (685001)</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
+        <is>
+          <t>PUSLATPUR AD (685001)</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6121,10 +6431,15 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418456)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418456)</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6211,10 +6526,15 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418458)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418458)</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6301,10 +6621,15 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR (656560)</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
+        <is>
+          <t>KPU OKUT (656560)</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6391,10 +6716,15 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR (553099)</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT (553099)</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6481,10 +6811,15 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR (597480)</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUT (597480)</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6571,10 +6906,15 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (662127)</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS (662127)</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6661,10 +7001,15 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR (691653)</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
+        <is>
+          <t>DISNAKERTRANS OKUT (691653)</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
